--- a/artfynd/A 7607-2021 artfynd.xlsx
+++ b/artfynd/A 7607-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356350</v>
+        <v>113356393</v>
       </c>
       <c r="B2" t="n">
-        <v>79195</v>
+        <v>96277</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>747726</v>
+        <v>747625</v>
       </c>
       <c r="R2" t="n">
-        <v>7202474</v>
+        <v>7202314</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356527</v>
+        <v>113356352</v>
       </c>
       <c r="B3" t="n">
-        <v>79194</v>
+        <v>79211</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>747641</v>
+        <v>747726</v>
       </c>
       <c r="R3" t="n">
-        <v>7202326</v>
+        <v>7202523</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356393</v>
+        <v>113356657</v>
       </c>
       <c r="B4" t="n">
-        <v>96261</v>
+        <v>90063</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>747625</v>
+        <v>747728</v>
       </c>
       <c r="R4" t="n">
-        <v>7202314</v>
+        <v>7202487</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356352</v>
+        <v>113356527</v>
       </c>
       <c r="B5" t="n">
-        <v>79195</v>
+        <v>79210</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>747726</v>
+        <v>747641</v>
       </c>
       <c r="R5" t="n">
-        <v>7202523</v>
+        <v>7202326</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113356657</v>
+        <v>113356353</v>
       </c>
       <c r="B6" t="n">
-        <v>90047</v>
+        <v>79211</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>747728</v>
+        <v>747686</v>
       </c>
       <c r="R6" t="n">
-        <v>7202487</v>
+        <v>7202476</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113356353</v>
+        <v>113356350</v>
       </c>
       <c r="B7" t="n">
-        <v>79195</v>
+        <v>79211</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>747686</v>
+        <v>747726</v>
       </c>
       <c r="R7" t="n">
-        <v>7202476</v>
+        <v>7202474</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 7607-2021 artfynd.xlsx
+++ b/artfynd/A 7607-2021 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356352</v>
+        <v>113356657</v>
       </c>
       <c r="B3" t="n">
-        <v>79211</v>
+        <v>90063</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>747726</v>
+        <v>747728</v>
       </c>
       <c r="R3" t="n">
-        <v>7202523</v>
+        <v>7202487</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356657</v>
+        <v>113356527</v>
       </c>
       <c r="B4" t="n">
-        <v>90063</v>
+        <v>79210</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6461</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>747728</v>
+        <v>747641</v>
       </c>
       <c r="R4" t="n">
-        <v>7202487</v>
+        <v>7202326</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356527</v>
+        <v>113356352</v>
       </c>
       <c r="B5" t="n">
-        <v>79210</v>
+        <v>79211</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>747641</v>
+        <v>747726</v>
       </c>
       <c r="R5" t="n">
-        <v>7202326</v>
+        <v>7202523</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 7607-2021 artfynd.xlsx
+++ b/artfynd/A 7607-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356393</v>
+        <v>113356353</v>
       </c>
       <c r="B2" t="n">
-        <v>96277</v>
+        <v>79211</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>747625</v>
+        <v>747686</v>
       </c>
       <c r="R2" t="n">
-        <v>7202314</v>
+        <v>7202476</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356657</v>
+        <v>113356527</v>
       </c>
       <c r="B3" t="n">
-        <v>90063</v>
+        <v>79210</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6461</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>747728</v>
+        <v>747641</v>
       </c>
       <c r="R3" t="n">
-        <v>7202487</v>
+        <v>7202326</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356527</v>
+        <v>113356393</v>
       </c>
       <c r="B4" t="n">
-        <v>79210</v>
+        <v>96277</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6461</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>747641</v>
+        <v>747625</v>
       </c>
       <c r="R4" t="n">
-        <v>7202326</v>
+        <v>7202314</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356352</v>
+        <v>113356657</v>
       </c>
       <c r="B5" t="n">
-        <v>79211</v>
+        <v>90063</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>747726</v>
+        <v>747728</v>
       </c>
       <c r="R5" t="n">
-        <v>7202523</v>
+        <v>7202487</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113356353</v>
+        <v>113356352</v>
       </c>
       <c r="B6" t="n">
         <v>79211</v>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>747686</v>
+        <v>747726</v>
       </c>
       <c r="R6" t="n">
-        <v>7202476</v>
+        <v>7202523</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 7607-2021 artfynd.xlsx
+++ b/artfynd/A 7607-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356353</v>
+        <v>113356657</v>
       </c>
       <c r="B2" t="n">
-        <v>79211</v>
+        <v>90075</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>747686</v>
+        <v>747728</v>
       </c>
       <c r="R2" t="n">
-        <v>7202476</v>
+        <v>7202487</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356527</v>
+        <v>113356353</v>
       </c>
       <c r="B3" t="n">
-        <v>79210</v>
+        <v>79223</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>747641</v>
+        <v>747686</v>
       </c>
       <c r="R3" t="n">
-        <v>7202326</v>
+        <v>7202476</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356393</v>
+        <v>113356352</v>
       </c>
       <c r="B4" t="n">
-        <v>96277</v>
+        <v>79223</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>747625</v>
+        <v>747726</v>
       </c>
       <c r="R4" t="n">
-        <v>7202314</v>
+        <v>7202523</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356657</v>
+        <v>113356393</v>
       </c>
       <c r="B5" t="n">
-        <v>90063</v>
+        <v>96289</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>747728</v>
+        <v>747625</v>
       </c>
       <c r="R5" t="n">
-        <v>7202487</v>
+        <v>7202314</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113356352</v>
+        <v>113356350</v>
       </c>
       <c r="B6" t="n">
-        <v>79211</v>
+        <v>79223</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
         <v>747726</v>
       </c>
       <c r="R6" t="n">
-        <v>7202523</v>
+        <v>7202474</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113356350</v>
+        <v>113356527</v>
       </c>
       <c r="B7" t="n">
-        <v>79211</v>
+        <v>79222</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>747726</v>
+        <v>747641</v>
       </c>
       <c r="R7" t="n">
-        <v>7202474</v>
+        <v>7202326</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 7607-2021 artfynd.xlsx
+++ b/artfynd/A 7607-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356657</v>
+        <v>113356527</v>
       </c>
       <c r="B2" t="n">
-        <v>90075</v>
+        <v>79222</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6461</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>747728</v>
+        <v>747641</v>
       </c>
       <c r="R2" t="n">
-        <v>7202487</v>
+        <v>7202326</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356352</v>
+        <v>113356350</v>
       </c>
       <c r="B4" t="n">
         <v>79223</v>
@@ -930,7 +930,7 @@
         <v>747726</v>
       </c>
       <c r="R4" t="n">
-        <v>7202523</v>
+        <v>7202474</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356393</v>
+        <v>113356657</v>
       </c>
       <c r="B5" t="n">
-        <v>96289</v>
+        <v>90075</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>747625</v>
+        <v>747728</v>
       </c>
       <c r="R5" t="n">
-        <v>7202314</v>
+        <v>7202487</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113356350</v>
+        <v>113356393</v>
       </c>
       <c r="B6" t="n">
-        <v>79223</v>
+        <v>96289</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>747726</v>
+        <v>747625</v>
       </c>
       <c r="R6" t="n">
-        <v>7202474</v>
+        <v>7202314</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113356527</v>
+        <v>113356352</v>
       </c>
       <c r="B7" t="n">
-        <v>79222</v>
+        <v>79223</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>747641</v>
+        <v>747726</v>
       </c>
       <c r="R7" t="n">
-        <v>7202326</v>
+        <v>7202523</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 7607-2021 artfynd.xlsx
+++ b/artfynd/A 7607-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113356527</v>
       </c>
       <c r="B2" t="n">
-        <v>79222</v>
+        <v>79244</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356353</v>
+        <v>113356393</v>
       </c>
       <c r="B3" t="n">
-        <v>79223</v>
+        <v>96311</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>747686</v>
+        <v>747625</v>
       </c>
       <c r="R3" t="n">
-        <v>7202476</v>
+        <v>7202314</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356350</v>
+        <v>113356353</v>
       </c>
       <c r="B4" t="n">
-        <v>79223</v>
+        <v>79245</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>747726</v>
+        <v>747686</v>
       </c>
       <c r="R4" t="n">
-        <v>7202474</v>
+        <v>7202476</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
         <v>113356657</v>
       </c>
       <c r="B5" t="n">
-        <v>90075</v>
+        <v>90097</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113356393</v>
+        <v>113356350</v>
       </c>
       <c r="B6" t="n">
-        <v>96289</v>
+        <v>79245</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>747625</v>
+        <v>747726</v>
       </c>
       <c r="R6" t="n">
-        <v>7202314</v>
+        <v>7202474</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1208,7 @@
         <v>113356352</v>
       </c>
       <c r="B7" t="n">
-        <v>79223</v>
+        <v>79245</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 7607-2021 artfynd.xlsx
+++ b/artfynd/A 7607-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356527</v>
+        <v>113356657</v>
       </c>
       <c r="B2" t="n">
-        <v>79244</v>
+        <v>90101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6461</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>747641</v>
+        <v>747728</v>
       </c>
       <c r="R2" t="n">
-        <v>7202326</v>
+        <v>7202487</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356393</v>
+        <v>113356353</v>
       </c>
       <c r="B3" t="n">
-        <v>96311</v>
+        <v>79249</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>747625</v>
+        <v>747686</v>
       </c>
       <c r="R3" t="n">
-        <v>7202314</v>
+        <v>7202476</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356353</v>
+        <v>113356350</v>
       </c>
       <c r="B4" t="n">
-        <v>79245</v>
+        <v>79249</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>747686</v>
+        <v>747726</v>
       </c>
       <c r="R4" t="n">
-        <v>7202476</v>
+        <v>7202474</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356657</v>
+        <v>113356352</v>
       </c>
       <c r="B5" t="n">
-        <v>90097</v>
+        <v>79249</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>747728</v>
+        <v>747726</v>
       </c>
       <c r="R5" t="n">
-        <v>7202487</v>
+        <v>7202523</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113356350</v>
+        <v>113356527</v>
       </c>
       <c r="B6" t="n">
-        <v>79245</v>
+        <v>79248</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>747726</v>
+        <v>747641</v>
       </c>
       <c r="R6" t="n">
-        <v>7202474</v>
+        <v>7202326</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113356352</v>
+        <v>113356393</v>
       </c>
       <c r="B7" t="n">
-        <v>79245</v>
+        <v>96315</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>747726</v>
+        <v>747625</v>
       </c>
       <c r="R7" t="n">
-        <v>7202523</v>
+        <v>7202314</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 7607-2021 artfynd.xlsx
+++ b/artfynd/A 7607-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356657</v>
+        <v>113356352</v>
       </c>
       <c r="B2" t="n">
-        <v>90101</v>
+        <v>79249</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>747728</v>
+        <v>747726</v>
       </c>
       <c r="R2" t="n">
-        <v>7202487</v>
+        <v>7202523</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356352</v>
+        <v>113356393</v>
       </c>
       <c r="B5" t="n">
-        <v>79249</v>
+        <v>96315</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>747726</v>
+        <v>747625</v>
       </c>
       <c r="R5" t="n">
-        <v>7202523</v>
+        <v>7202314</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113356527</v>
+        <v>113356657</v>
       </c>
       <c r="B6" t="n">
-        <v>79248</v>
+        <v>90101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6461</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>747641</v>
+        <v>747728</v>
       </c>
       <c r="R6" t="n">
-        <v>7202326</v>
+        <v>7202487</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113356393</v>
+        <v>113356527</v>
       </c>
       <c r="B7" t="n">
-        <v>96315</v>
+        <v>79248</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>747625</v>
+        <v>747641</v>
       </c>
       <c r="R7" t="n">
-        <v>7202314</v>
+        <v>7202326</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 7607-2021 artfynd.xlsx
+++ b/artfynd/A 7607-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356352</v>
+        <v>113356527</v>
       </c>
       <c r="B2" t="n">
-        <v>79249</v>
+        <v>79254</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>747726</v>
+        <v>747641</v>
       </c>
       <c r="R2" t="n">
-        <v>7202523</v>
+        <v>7202326</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,7 +784,7 @@
         <v>113356353</v>
       </c>
       <c r="B3" t="n">
-        <v>79249</v>
+        <v>79255</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356350</v>
+        <v>113356393</v>
       </c>
       <c r="B4" t="n">
-        <v>79249</v>
+        <v>96321</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>747726</v>
+        <v>747625</v>
       </c>
       <c r="R4" t="n">
-        <v>7202474</v>
+        <v>7202314</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356393</v>
+        <v>113356657</v>
       </c>
       <c r="B5" t="n">
-        <v>96315</v>
+        <v>90107</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>747625</v>
+        <v>747728</v>
       </c>
       <c r="R5" t="n">
-        <v>7202314</v>
+        <v>7202487</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113356657</v>
+        <v>113356352</v>
       </c>
       <c r="B6" t="n">
-        <v>90101</v>
+        <v>79255</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>747728</v>
+        <v>747726</v>
       </c>
       <c r="R6" t="n">
-        <v>7202487</v>
+        <v>7202523</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113356527</v>
+        <v>113356350</v>
       </c>
       <c r="B7" t="n">
-        <v>79248</v>
+        <v>79255</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>747641</v>
+        <v>747726</v>
       </c>
       <c r="R7" t="n">
-        <v>7202326</v>
+        <v>7202474</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 7607-2021 artfynd.xlsx
+++ b/artfynd/A 7607-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356527</v>
+        <v>113356657</v>
       </c>
       <c r="B2" t="n">
-        <v>79254</v>
+        <v>90107</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6461</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>747641</v>
+        <v>747728</v>
       </c>
       <c r="R2" t="n">
-        <v>7202326</v>
+        <v>7202487</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356353</v>
+        <v>113356393</v>
       </c>
       <c r="B3" t="n">
-        <v>79255</v>
+        <v>96321</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>747686</v>
+        <v>747625</v>
       </c>
       <c r="R3" t="n">
-        <v>7202476</v>
+        <v>7202314</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356393</v>
+        <v>113356353</v>
       </c>
       <c r="B4" t="n">
-        <v>96321</v>
+        <v>79255</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>747625</v>
+        <v>747686</v>
       </c>
       <c r="R4" t="n">
-        <v>7202314</v>
+        <v>7202476</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356657</v>
+        <v>113356352</v>
       </c>
       <c r="B5" t="n">
-        <v>90107</v>
+        <v>79255</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>747728</v>
+        <v>747726</v>
       </c>
       <c r="R5" t="n">
-        <v>7202487</v>
+        <v>7202523</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113356352</v>
+        <v>113356527</v>
       </c>
       <c r="B6" t="n">
-        <v>79255</v>
+        <v>79254</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>747726</v>
+        <v>747641</v>
       </c>
       <c r="R6" t="n">
-        <v>7202523</v>
+        <v>7202326</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 7607-2021 artfynd.xlsx
+++ b/artfynd/A 7607-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356657</v>
+        <v>113356353</v>
       </c>
       <c r="B2" t="n">
-        <v>90107</v>
+        <v>79262</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>747728</v>
+        <v>747686</v>
       </c>
       <c r="R2" t="n">
-        <v>7202487</v>
+        <v>7202476</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356393</v>
+        <v>113356350</v>
       </c>
       <c r="B3" t="n">
-        <v>96321</v>
+        <v>79262</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>747625</v>
+        <v>747726</v>
       </c>
       <c r="R3" t="n">
-        <v>7202314</v>
+        <v>7202474</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356353</v>
+        <v>113356657</v>
       </c>
       <c r="B4" t="n">
-        <v>79255</v>
+        <v>90114</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>747686</v>
+        <v>747728</v>
       </c>
       <c r="R4" t="n">
-        <v>7202476</v>
+        <v>7202487</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
         <v>113356352</v>
       </c>
       <c r="B5" t="n">
-        <v>79255</v>
+        <v>79262</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>113356527</v>
       </c>
       <c r="B6" t="n">
-        <v>79254</v>
+        <v>79261</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113356350</v>
+        <v>113356393</v>
       </c>
       <c r="B7" t="n">
-        <v>79255</v>
+        <v>96328</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>747726</v>
+        <v>747625</v>
       </c>
       <c r="R7" t="n">
-        <v>7202474</v>
+        <v>7202314</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 7607-2021 artfynd.xlsx
+++ b/artfynd/A 7607-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356353</v>
+        <v>113356350</v>
       </c>
       <c r="B2" t="n">
-        <v>79262</v>
+        <v>79264</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>747686</v>
+        <v>747726</v>
       </c>
       <c r="R2" t="n">
-        <v>7202476</v>
+        <v>7202474</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356350</v>
+        <v>113356527</v>
       </c>
       <c r="B3" t="n">
-        <v>79262</v>
+        <v>79263</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>747726</v>
+        <v>747641</v>
       </c>
       <c r="R3" t="n">
-        <v>7202474</v>
+        <v>7202326</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356657</v>
+        <v>113356353</v>
       </c>
       <c r="B4" t="n">
-        <v>90114</v>
+        <v>79264</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>747728</v>
+        <v>747686</v>
       </c>
       <c r="R4" t="n">
-        <v>7202487</v>
+        <v>7202476</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356352</v>
+        <v>113356393</v>
       </c>
       <c r="B5" t="n">
-        <v>79262</v>
+        <v>96333</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>747726</v>
+        <v>747625</v>
       </c>
       <c r="R5" t="n">
-        <v>7202523</v>
+        <v>7202314</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113356527</v>
+        <v>113356657</v>
       </c>
       <c r="B6" t="n">
-        <v>79261</v>
+        <v>90117</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6461</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>747641</v>
+        <v>747728</v>
       </c>
       <c r="R6" t="n">
-        <v>7202326</v>
+        <v>7202487</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113356393</v>
+        <v>113356352</v>
       </c>
       <c r="B7" t="n">
-        <v>96328</v>
+        <v>79264</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>747625</v>
+        <v>747726</v>
       </c>
       <c r="R7" t="n">
-        <v>7202314</v>
+        <v>7202523</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 7607-2021 artfynd.xlsx
+++ b/artfynd/A 7607-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113356350</v>
       </c>
       <c r="B2" t="n">
-        <v>79264</v>
+        <v>79292</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356527</v>
+        <v>113356657</v>
       </c>
       <c r="B3" t="n">
-        <v>79263</v>
+        <v>90148</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6461</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>747641</v>
+        <v>747728</v>
       </c>
       <c r="R3" t="n">
-        <v>7202326</v>
+        <v>7202487</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356353</v>
+        <v>113356352</v>
       </c>
       <c r="B4" t="n">
-        <v>79264</v>
+        <v>79292</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>747686</v>
+        <v>747726</v>
       </c>
       <c r="R4" t="n">
-        <v>7202476</v>
+        <v>7202523</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
         <v>113356393</v>
       </c>
       <c r="B5" t="n">
-        <v>96333</v>
+        <v>96361</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113356657</v>
+        <v>113356527</v>
       </c>
       <c r="B6" t="n">
-        <v>90117</v>
+        <v>79291</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6461</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>747728</v>
+        <v>747641</v>
       </c>
       <c r="R6" t="n">
-        <v>7202487</v>
+        <v>7202326</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113356352</v>
+        <v>113356353</v>
       </c>
       <c r="B7" t="n">
-        <v>79264</v>
+        <v>79292</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>747726</v>
+        <v>747686</v>
       </c>
       <c r="R7" t="n">
-        <v>7202523</v>
+        <v>7202476</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 7607-2021 artfynd.xlsx
+++ b/artfynd/A 7607-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356350</v>
+        <v>113356352</v>
       </c>
       <c r="B2" t="n">
         <v>79292</v>
@@ -718,7 +718,7 @@
         <v>747726</v>
       </c>
       <c r="R2" t="n">
-        <v>7202474</v>
+        <v>7202523</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356657</v>
+        <v>113356350</v>
       </c>
       <c r="B3" t="n">
-        <v>90148</v>
+        <v>79292</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>747728</v>
+        <v>747726</v>
       </c>
       <c r="R3" t="n">
-        <v>7202487</v>
+        <v>7202474</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356352</v>
+        <v>113356353</v>
       </c>
       <c r="B4" t="n">
         <v>79292</v>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>747726</v>
+        <v>747686</v>
       </c>
       <c r="R4" t="n">
-        <v>7202523</v>
+        <v>7202476</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356393</v>
+        <v>113356527</v>
       </c>
       <c r="B5" t="n">
-        <v>96361</v>
+        <v>79291</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>747625</v>
+        <v>747641</v>
       </c>
       <c r="R5" t="n">
-        <v>7202314</v>
+        <v>7202326</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113356527</v>
+        <v>113356657</v>
       </c>
       <c r="B6" t="n">
-        <v>79291</v>
+        <v>90149</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6461</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>747641</v>
+        <v>747728</v>
       </c>
       <c r="R6" t="n">
-        <v>7202326</v>
+        <v>7202487</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113356353</v>
+        <v>113356393</v>
       </c>
       <c r="B7" t="n">
-        <v>79292</v>
+        <v>96361</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>747686</v>
+        <v>747625</v>
       </c>
       <c r="R7" t="n">
-        <v>7202476</v>
+        <v>7202314</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 7607-2021 artfynd.xlsx
+++ b/artfynd/A 7607-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
